--- a/data/fred_api_data.xlsx
+++ b/data/fred_api_data.xlsx
@@ -2184,7 +2184,7 @@
         <v>0.04082608636665808</v>
       </c>
       <c r="C135" t="n">
-        <v>0.07306001295559161</v>
+        <v>0.0736088087997786</v>
       </c>
     </row>
     <row r="136">
@@ -2197,7 +2197,7 @@
         <v>0.05030681069019738</v>
       </c>
       <c r="C136" t="n">
-        <v>0.0009964570416296503</v>
+        <v>-0.01200066749274831</v>
       </c>
     </row>
   </sheetData>

--- a/data/fred_api_data.xlsx
+++ b/data/fred_api_data.xlsx
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.09512343730500716</v>
+        <v>0.09435264235848573</v>
       </c>
       <c r="C90" t="n">
         <v>0.07701907648422179</v>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.09170873214760134</v>
+        <v>0.09241241643749065</v>
       </c>
       <c r="C91" t="n">
         <v>-0.02880202563696777</v>
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.07923658543440992</v>
+        <v>0.07958793602608427</v>
       </c>
       <c r="C92" t="n">
         <v>-0.09767862526379256</v>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.06365657089089205</v>
+        <v>0.06399749082925377</v>
       </c>
       <c r="C93" t="n">
         <v>-0.1541307028360049</v>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.0586401753574517</v>
+        <v>0.05864793796452816</v>
       </c>
       <c r="C94" t="n">
         <v>-0.1196821718258567</v>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.04879011306309566</v>
+        <v>0.04846289857168218</v>
       </c>
       <c r="C95" t="n">
         <v>-0.09206452664168163</v>
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.04930201062610684</v>
+        <v>0.04896051655232569</v>
       </c>
       <c r="C96" t="n">
         <v>-0.0968927497494152</v>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.04881472839395373</v>
+        <v>0.0481069927201887</v>
       </c>
       <c r="C97" t="n">
         <v>-0.07999271137026231</v>
@@ -1700,7 +1700,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.06577006123004647</v>
+        <v>0.06612638528947712</v>
       </c>
       <c r="C98" t="n">
         <v>-0.0417450169236554</v>
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.05577052120634396</v>
+        <v>0.05609679643909482</v>
       </c>
       <c r="C99" t="n">
         <v>0.01022972002871492</v>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.04925041574623346</v>
+        <v>0.04958549480006957</v>
       </c>
       <c r="C100" t="n">
         <v>0.02719200887902318</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.05660308166221517</v>
+        <v>0.05697777506037727</v>
       </c>
       <c r="C101" t="n">
         <v>0.03842345018815618</v>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.04422039497136332</v>
+        <v>0.03944607886838436</v>
       </c>
       <c r="C102" t="n">
         <v>0.04120879120879128</v>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.05788535788535798</v>
+        <v>0.04687221740730618</v>
       </c>
       <c r="C103" t="n">
         <v>-0.02842423165748809</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.07961299403286959</v>
+        <v>0.06427545271272916</v>
       </c>
       <c r="C104" t="n">
         <v>-0.05186385737439214</v>
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.04668718257227811</v>
+        <v>0.02941448685169545</v>
       </c>
       <c r="C105" t="n">
         <v>-0.002479496471485598</v>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.0346383399996586</v>
+        <v>0.02158474944537203</v>
       </c>
       <c r="C106" t="n">
         <v>-0.01017715793441376</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.04983295432213142</v>
+        <v>0.03825827596765596</v>
       </c>
       <c r="C107" t="n">
         <v>0.01773633205339187</v>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.05478348990715132</v>
+        <v>0.04381759703142452</v>
       </c>
       <c r="C108" t="n">
         <v>0.04691358024691361</v>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.08551769874823845</v>
+        <v>0.07232564804252672</v>
       </c>
       <c r="C109" t="n">
         <v>0.0642447418738048</v>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.001242803015722105</v>
+        <v>-0.01350557181796308</v>
       </c>
       <c r="C110" t="n">
         <v>0.01408987052551369</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>-0.3396694656896828</v>
+        <v>-0.3513361478091327</v>
       </c>
       <c r="C111" t="n">
         <v>0.1611570247933882</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-0.1167764182887057</v>
+        <v>-0.1356841416232498</v>
       </c>
       <c r="C112" t="n">
         <v>-0.04807692307692313</v>
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-0.1507338903059277</v>
+        <v>-0.16594875019651</v>
       </c>
       <c r="C113" t="n">
         <v>-0.01616960114983834</v>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-0.02409473123417527</v>
+        <v>-0.0392785411962282</v>
       </c>
       <c r="C114" t="n">
         <v>0.06027037176117189</v>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.6786784597689977</v>
+        <v>0.6542674558604373</v>
       </c>
       <c r="C115" t="n">
         <v>0.07535200371344586</v>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.2894278826365615</v>
+        <v>0.2805167137693876</v>
       </c>
       <c r="C116" t="n">
         <v>0.3789212883552504</v>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.3168417140253699</v>
+        <v>0.3102248024025835</v>
       </c>
       <c r="C117" t="n">
         <v>0.24509130752374</v>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.2500590930067648</v>
+        <v>0.2473203370912591</v>
       </c>
       <c r="C118" t="n">
         <v>0.1806445900478129</v>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.1570930215726671</v>
+        <v>0.1558639854640953</v>
       </c>
       <c r="C119" t="n">
         <v>-0.03496834532374105</v>
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.117504890716986</v>
+        <v>0.1066740395249315</v>
       </c>
       <c r="C120" t="n">
         <v>-0.0786502100840335</v>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.1354152914665514</v>
+        <v>0.1076686263414821</v>
       </c>
       <c r="C121" t="n">
         <v>-0.04713176066129665</v>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.1729576171224305</v>
+        <v>0.1256758676199043</v>
       </c>
       <c r="C122" t="n">
         <v>0.00128391654542459</v>
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.09537510789746917</v>
+        <v>0.03720778677516368</v>
       </c>
       <c r="C123" t="n">
         <v>0.03865829129994625</v>
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.0984122320565084</v>
+        <v>0.03675783710977387</v>
       </c>
       <c r="C124" t="n">
         <v>0.07611739909843007</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.1002441752769525</v>
+        <v>0.0469455519912032</v>
       </c>
       <c r="C125" t="n">
         <v>0.1063220646567447</v>
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.05651064156447316</v>
+        <v>0.02186293395694716</v>
       </c>
       <c r="C126" t="n">
         <v>0.07507871880832728</v>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.05373396831922883</v>
+        <v>0.03141968049653365</v>
       </c>
       <c r="C127" t="n">
         <v>0.06973335725820906</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.04295299021465349</v>
+        <v>0.02930662364059256</v>
       </c>
       <c r="C128" t="n">
         <v>0.04782980835178074</v>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.04433463429210716</v>
+        <v>0.03652903839394628</v>
       </c>
       <c r="C129" t="n">
         <v>0.05754279640265358</v>
@@ -2116,7 +2116,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.04982598144286454</v>
+        <v>0.04168313082419584</v>
       </c>
       <c r="C130" t="n">
         <v>0.07674247512143184</v>
@@ -2129,7 +2129,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.06516665582843806</v>
+        <v>0.06478592655399784</v>
       </c>
       <c r="C131" t="n">
         <v>0.07099810387236771</v>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.06127733846263439</v>
+        <v>0.05849158007882482</v>
       </c>
       <c r="C132" t="n">
         <v>0.1458158998599113</v>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.04624902731881964</v>
+        <v>0.04303284410916386</v>
       </c>
       <c r="C133" t="n">
         <v>0.1177578011632512</v>
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.03828039297789076</v>
+        <v>0.03670395410128857</v>
       </c>
       <c r="C134" t="n">
         <v>0.1025346710440331</v>
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.04082608636665808</v>
+        <v>0.03727570024816962</v>
       </c>
       <c r="C135" t="n">
         <v>0.0736088087997786</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.05030681069019738</v>
+        <v>0.05182123034227559</v>
       </c>
       <c r="C136" t="n">
         <v>-0.01200066749274831</v>
